--- a/docs/RPG_0.1.xlsx
+++ b/docs/RPG_0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sonstiges\3D RPG\game\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1E51E2-8CF9-4C2E-8C71-4616DD52C833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A84110-B90B-44D4-85F2-33B9373C8591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{4BE2A854-3C52-4E67-A093-93255C02F786}"/>
+    <workbookView xWindow="9345" yWindow="3465" windowWidth="28800" windowHeight="11235" xr2:uid="{4BE2A854-3C52-4E67-A093-93255C02F786}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="161">
   <si>
     <t>False</t>
   </si>
@@ -126,9 +126,6 @@
   </si>
   <si>
     <t>Werewolf</t>
-  </si>
-  <si>
-    <t>both</t>
   </si>
   <si>
     <t>Poison</t>
@@ -647,10 +644,6 @@
   </cellStyles>
   <dxfs count="10">
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -661,6 +654,10 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -725,21 +722,21 @@
     <tableColumn id="39" xr3:uid="{FE9BCC63-A58F-4EE4-AEF0-714F5229CD56}" name="entity 8l: _x000a_regeneration_per_turn_in_percent_of total_life"/>
     <tableColumn id="40" xr3:uid="{20EFEFED-5BC7-4680-8D94-F0FFDF66C696}" name="entity 8m: _x000a_steal_mana_on_hit_in_percent_of_characters_max_mana"/>
     <tableColumn id="41" xr3:uid="{6B83D3CE-7E9F-4FEC-A9B7-E09FF7C7DABE}" name="entity 8n: _x000a_increases_magical_age_by_1_year_on_hit"/>
-    <tableColumn id="10" xr3:uid="{657AB867-1E43-41EC-95BE-4DF86DC71643}" name="entity 9:_x000a_outside_spawner_hut_xp" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{657AB867-1E43-41EC-95BE-4DF86DC71643}" name="entity 9:_x000a_outside_spawner_hut_xp" dataDxfId="4"/>
     <tableColumn id="11" xr3:uid="{C864C4B0-6F86-4266-84B7-0009F0740F0B}" name="entity 10:_x000a_res_magic"/>
     <tableColumn id="12" xr3:uid="{4DE80521-738A-490D-8660-B2E4BE035E51}" name="entity 11:_x000a_res_fire"/>
     <tableColumn id="13" xr3:uid="{FEFD4387-19A1-41A1-9279-3622879EEEF7}" name="entity 12:_x000a_res_physical"/>
     <tableColumn id="15" xr3:uid="{9D486DD9-3A76-4B9D-A48E-45B8AC5A9204}" name="entity 13:_x000a_res_cold"/>
     <tableColumn id="16" xr3:uid="{674684F8-3D91-4BFB-A915-BAFCD2C82B25}" name="entity 14:_x000a_res_poison"/>
     <tableColumn id="18" xr3:uid="{4F25CA0D-398A-4ADE-B1B4-5F0BB7C038DA}" name="entity 15:_x000a_exp_old (not used anymore)"/>
-    <tableColumn id="27" xr3:uid="{BB0197D4-3C5C-4D64-BB3F-0966359DE0DF}" name="entity 16:_x000a_gold" dataDxfId="4"/>
+    <tableColumn id="27" xr3:uid="{BB0197D4-3C5C-4D64-BB3F-0966359DE0DF}" name="entity 16:_x000a_gold" dataDxfId="3"/>
     <tableColumn id="25" xr3:uid="{ED29C8D4-1AB4-48DC-AD5F-5B5BCA75AC90}" name="entity 17:_x000a_treasure_level_old (not used anymore)"/>
-    <tableColumn id="6" xr3:uid="{306F37DE-3F0E-4874-9CA6-CA8E4537DAC0}" name="entity 18:_x000a_icon_height" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{306F37DE-3F0E-4874-9CA6-CA8E4537DAC0}" name="entity 18:_x000a_icon_height" dataDxfId="2"/>
     <tableColumn id="7" xr3:uid="{06CC750E-0BC9-4044-ADAB-702E10B69198}" name="entity 19:_x000a_terrain"/>
     <tableColumn id="14" xr3:uid="{10A0D880-46D4-4EF1-9E97-94B8F7FF7F8A}" name="entity 20:_x000a_undead"/>
     <tableColumn id="17" xr3:uid="{5C125C46-427D-41B4-A8E2-C627B813F7BF}" name="entity 21:_x000a_final_boss"/>
     <tableColumn id="19" xr3:uid="{0A20AB78-3403-450A-92F0-E11B2C907395}" name="entity 22: group"/>
-    <tableColumn id="9" xr3:uid="{4D1BFE81-E36F-433A-9F94-15DAEEA44F00}" name="entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)" dataDxfId="2">
+    <tableColumn id="9" xr3:uid="{4D1BFE81-E36F-433A-9F94-15DAEEA44F00}" name="entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)" dataDxfId="1">
       <calculatedColumnFormula>(_csv247[[#This Row],[entity 1:
 health]]*_csv247[[#This Row],[entity 2:
 armor]]+_csv247[[#This Row],[entity 1:
@@ -758,7 +755,7 @@
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{8A88862A-3CB6-4053-9301-EB3CFDFFA903}" name="entity 24: treasure_level_new" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{8A88862A-3CB6-4053-9301-EB3CFDFFA903}" name="entity 24: treasure_level_new" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1092,124 +1089,124 @@
   <sheetData>
     <row r="1" spans="1:40" s="3" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y1" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AE1" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AJ1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK1" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y1" s="9" t="s">
+      <c r="AL1" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM1" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="Z1" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="AE1" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="AG1" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="AH1" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI1" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ1" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="AK1" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL1" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="AM1" s="8" t="s">
-        <v>158</v>
-      </c>
       <c r="AN1" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.25">
@@ -1217,7 +1214,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C2">
         <v>15</v>
@@ -1241,7 +1238,7 @@
         <v>6</v>
       </c>
       <c r="J2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y2" s="10" t="s">
         <v>2</v>
@@ -1280,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="AL2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM2" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -1311,7 +1308,7 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -1335,7 +1332,7 @@
         <v>3</v>
       </c>
       <c r="J3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y3" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -1375,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="AL3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM3" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -1406,7 +1403,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -1430,7 +1427,7 @@
         <v>3</v>
       </c>
       <c r="L4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y4" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -1470,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM4" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -1501,7 +1498,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C5">
         <v>25</v>
@@ -1525,7 +1522,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y5" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -1565,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="AL5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AM5" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -1596,7 +1593,7 @@
         <v>64</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6">
         <v>20</v>
@@ -1620,7 +1617,7 @@
         <v>3</v>
       </c>
       <c r="Y6" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z6" s="2">
         <v>0.17</v>
@@ -1656,7 +1653,7 @@
         <v>18</v>
       </c>
       <c r="AL6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AM6" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -1687,7 +1684,7 @@
         <v>62</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -1711,7 +1708,7 @@
         <v>6</v>
       </c>
       <c r="O7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y7" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -1751,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="AL7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM7" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -1782,7 +1779,7 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C8">
         <v>35</v>
@@ -1806,10 +1803,10 @@
         <v>3</v>
       </c>
       <c r="P8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z8" s="2">
         <v>0.25</v>
@@ -1845,7 +1842,7 @@
         <v>18</v>
       </c>
       <c r="AL8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AM8" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -1876,7 +1873,7 @@
         <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9">
         <v>25</v>
@@ -1900,7 +1897,7 @@
         <v>3</v>
       </c>
       <c r="J9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y9" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -1940,7 +1937,7 @@
         <v>0</v>
       </c>
       <c r="AL9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM9" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -1971,7 +1968,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10">
         <v>40</v>
@@ -1995,10 +1992,10 @@
         <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z10" s="2">
         <v>0.2</v>
@@ -2034,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="AL10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AM10" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -2065,7 +2062,7 @@
         <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -2122,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="AL11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM11" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -2153,7 +2150,7 @@
         <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12">
         <v>15</v>
@@ -2177,7 +2174,7 @@
         <v>6</v>
       </c>
       <c r="M12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y12" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -2217,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="AL12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM12" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -2248,7 +2245,7 @@
         <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13">
         <v>50</v>
@@ -2269,13 +2266,13 @@
         <v>12</v>
       </c>
       <c r="I13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z13" s="2">
         <v>0.1</v>
@@ -2311,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM13" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -2342,7 +2339,7 @@
         <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -2366,7 +2363,7 @@
         <v>3</v>
       </c>
       <c r="O14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z14" s="2">
         <v>0.5</v>
@@ -2402,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="AL14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM14" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -2433,7 +2430,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C15">
         <v>40</v>
@@ -2457,7 +2454,7 @@
         <v>3</v>
       </c>
       <c r="M15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y15" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -2497,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="AL15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM15" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -2528,7 +2525,7 @@
         <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C16">
         <v>40</v>
@@ -2589,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="AL16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM16" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -2620,7 +2617,7 @@
         <v>77</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -2644,13 +2641,13 @@
         <v>6</v>
       </c>
       <c r="J17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z17" s="2">
         <v>0.5</v>
@@ -2686,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AL17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM17" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -2717,7 +2714,7 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C18">
         <v>70</v>
@@ -2741,10 +2738,10 @@
         <v>14</v>
       </c>
       <c r="J18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z18" s="2">
         <v>0.33</v>
@@ -2780,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="AL18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM18" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -2811,7 +2808,7 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C19">
         <v>30</v>
@@ -2835,7 +2832,7 @@
         <v>3</v>
       </c>
       <c r="L19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y19" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -2875,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="AL19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM19" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -2906,7 +2903,7 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20">
         <v>50</v>
@@ -2930,7 +2927,7 @@
         <v>3</v>
       </c>
       <c r="L20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y20" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -2970,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="AL20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM20" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3001,7 +2998,7 @@
         <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C21">
         <v>60</v>
@@ -3025,7 +3022,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y21" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -3065,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="AL21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM21" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3096,7 +3093,7 @@
         <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -3117,13 +3114,13 @@
         <v>12</v>
       </c>
       <c r="I22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y22" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z22" s="2">
         <v>0.4</v>
@@ -3159,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="AL22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM22" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3190,7 +3187,7 @@
         <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23">
         <v>45</v>
@@ -3251,7 +3248,7 @@
         <v>0</v>
       </c>
       <c r="AL23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM23" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3282,7 +3279,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C24">
         <v>75</v>
@@ -3306,10 +3303,10 @@
         <v>3</v>
       </c>
       <c r="O24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y24" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z24" s="2">
         <v>0</v>
@@ -3345,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="AL24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM24" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3376,7 +3373,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C25">
         <v>75</v>
@@ -3400,7 +3397,7 @@
         <v>3</v>
       </c>
       <c r="Q25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z25" s="2">
         <v>0.2</v>
@@ -3436,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="AL25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM25" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3467,7 +3464,7 @@
         <v>63</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C26">
         <v>50</v>
@@ -3491,7 +3488,7 @@
         <v>3</v>
       </c>
       <c r="L26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y26" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -3531,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="AL26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM26" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3562,7 +3559,7 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C27">
         <v>70</v>
@@ -3586,7 +3583,7 @@
         <v>3</v>
       </c>
       <c r="Y27" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z27" s="2">
         <v>0.17</v>
@@ -3622,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="AL27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM27" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3653,7 +3650,7 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C28">
         <v>50</v>
@@ -3677,7 +3674,7 @@
         <v>3</v>
       </c>
       <c r="N28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z28" s="2">
         <v>0.5</v>
@@ -3713,7 +3710,7 @@
         <v>0</v>
       </c>
       <c r="AL28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM28" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3744,7 +3741,7 @@
         <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C29">
         <v>50</v>
@@ -3768,7 +3765,7 @@
         <v>6</v>
       </c>
       <c r="X29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z29" s="2">
         <v>0.2</v>
@@ -3804,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="AL29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AM29" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3835,7 +3832,7 @@
         <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C30">
         <v>40</v>
@@ -3859,7 +3856,7 @@
         <v>3</v>
       </c>
       <c r="Y30" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z30" s="2">
         <v>0</v>
@@ -3895,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="AL30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM30" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3926,7 +3923,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C31">
         <v>60</v>
@@ -3987,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="AL31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM31" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -4018,7 +4015,7 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -4042,10 +4039,10 @@
         <v>6</v>
       </c>
       <c r="J32" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K32" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z32" s="2">
         <v>7.0000000000000007E-2</v>
@@ -4081,7 +4078,7 @@
         <v>0</v>
       </c>
       <c r="AL32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM32" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -4112,7 +4109,7 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C33">
         <v>40</v>
@@ -4169,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="AL33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM33" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -4200,7 +4197,7 @@
         <v>66</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -4224,7 +4221,7 @@
         <v>16</v>
       </c>
       <c r="J34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z34" s="2">
         <v>0</v>
@@ -4260,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="AL34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM34" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -4291,7 +4288,7 @@
         <v>91</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C35">
         <v>250</v>
@@ -4348,10 +4345,10 @@
         <v>0</v>
       </c>
       <c r="AK35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AL35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM35" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -4382,7 +4379,7 @@
         <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C36">
         <v>125</v>
@@ -4439,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="AL36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM36" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -4470,7 +4467,7 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -4494,7 +4491,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y37" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -4534,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="AL37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM37" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -4565,7 +4562,7 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -4589,7 +4586,7 @@
         <v>6</v>
       </c>
       <c r="X38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z38" s="2">
         <v>0.15</v>
@@ -4625,7 +4622,7 @@
         <v>18</v>
       </c>
       <c r="AL38" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AM38" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -4656,7 +4653,7 @@
         <v>65</v>
       </c>
       <c r="B39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>75</v>
@@ -4713,7 +4710,7 @@
         <v>0</v>
       </c>
       <c r="AL39" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM39" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -4744,7 +4741,7 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -4768,7 +4765,7 @@
         <v>3</v>
       </c>
       <c r="J40" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y40" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -4808,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="AL40" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM40" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -4839,7 +4836,7 @@
         <v>71</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C41">
         <v>150</v>
@@ -4863,7 +4860,7 @@
         <v>3</v>
       </c>
       <c r="Y41" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z41" s="2">
         <v>0.9</v>
@@ -4899,7 +4896,7 @@
         <v>0</v>
       </c>
       <c r="AL41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AM41" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -4930,7 +4927,7 @@
         <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C42">
         <v>75</v>
@@ -4954,7 +4951,7 @@
         <v>14</v>
       </c>
       <c r="Y42" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z42" s="2">
         <v>0.27</v>
@@ -4990,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="AL42" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM42" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5021,7 +5018,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C43">
         <v>150</v>
@@ -5045,10 +5042,10 @@
         <v>14</v>
       </c>
       <c r="J43" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y43" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z43" s="2">
         <v>0.05</v>
@@ -5084,7 +5081,7 @@
         <v>0</v>
       </c>
       <c r="AL43" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM43" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5115,7 +5112,7 @@
         <v>24</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -5139,7 +5136,7 @@
         <v>3</v>
       </c>
       <c r="J44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y44" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -5179,7 +5176,7 @@
         <v>0</v>
       </c>
       <c r="AL44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM44" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5210,7 +5207,7 @@
         <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C45">
         <v>125</v>
@@ -5274,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AL45" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM45" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5305,7 +5302,7 @@
         <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>50</v>
@@ -5365,7 +5362,7 @@
         <v>0</v>
       </c>
       <c r="AL46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM46" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5396,7 +5393,7 @@
         <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>100</v>
@@ -5420,7 +5417,7 @@
         <v>3</v>
       </c>
       <c r="P47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y47" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -5460,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="AL47" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM47" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5491,7 +5488,7 @@
         <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C48">
         <v>125</v>
@@ -5515,10 +5512,10 @@
         <v>3</v>
       </c>
       <c r="T48" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y48" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z48" s="2">
         <v>0.1</v>
@@ -5554,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="AL48" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM48" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5585,7 +5582,7 @@
         <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49">
         <v>150</v>
@@ -5609,7 +5606,7 @@
         <v>6</v>
       </c>
       <c r="J49" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z49" s="2">
         <v>0.1</v>
@@ -5645,7 +5642,7 @@
         <v>18</v>
       </c>
       <c r="AL49" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AM49" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5676,7 +5673,7 @@
         <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C50">
         <v>175</v>
@@ -5700,7 +5697,7 @@
         <v>3</v>
       </c>
       <c r="J50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y50" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -5740,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="AL50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM50" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5771,7 +5768,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C51">
         <v>125</v>
@@ -5795,7 +5792,7 @@
         <v>3</v>
       </c>
       <c r="O51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z51" s="2">
         <v>0.1</v>
@@ -5831,7 +5828,7 @@
         <v>0</v>
       </c>
       <c r="AL51" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM51" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5862,7 +5859,7 @@
         <v>23</v>
       </c>
       <c r="B52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C52">
         <v>100</v>
@@ -5886,7 +5883,7 @@
         <v>6</v>
       </c>
       <c r="O52" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z52" s="2">
         <v>0.9</v>
@@ -5922,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="AL52" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM52" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5953,7 +5950,7 @@
         <v>44</v>
       </c>
       <c r="B53" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C53">
         <v>150</v>
@@ -5977,7 +5974,7 @@
         <v>14</v>
       </c>
       <c r="J53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y53" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
@@ -6017,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="AL53" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM53" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6048,7 +6045,7 @@
         <v>67</v>
       </c>
       <c r="B54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C54">
         <v>100</v>
@@ -6105,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="AL54" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM54" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6136,7 +6133,7 @@
         <v>59</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C55">
         <v>200</v>
@@ -6193,7 +6190,7 @@
         <v>0</v>
       </c>
       <c r="AL55" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM55" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6224,7 +6221,7 @@
         <v>38</v>
       </c>
       <c r="B56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C56">
         <v>200</v>
@@ -6248,7 +6245,7 @@
         <v>6</v>
       </c>
       <c r="S56" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z56" s="2">
         <v>0.5</v>
@@ -6284,7 +6281,7 @@
         <v>18</v>
       </c>
       <c r="AL56" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AM56" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6315,7 +6312,7 @@
         <v>47</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C57">
         <v>250</v>
@@ -6339,7 +6336,7 @@
         <v>3</v>
       </c>
       <c r="P57" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z57" s="2">
         <v>0.6</v>
@@ -6375,7 +6372,7 @@
         <v>0</v>
       </c>
       <c r="AL57" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AM57" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6406,7 +6403,7 @@
         <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C58">
         <v>300</v>
@@ -6427,10 +6424,10 @@
         <v>200</v>
       </c>
       <c r="I58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L58" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z58" s="2">
         <v>0.1</v>
@@ -6466,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="AL58" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM58" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6497,7 +6494,7 @@
         <v>34</v>
       </c>
       <c r="B59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C59">
         <v>250</v>
@@ -6554,7 +6551,7 @@
         <v>0</v>
       </c>
       <c r="AL59" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM59" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6585,7 +6582,7 @@
         <v>54</v>
       </c>
       <c r="B60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C60">
         <v>175</v>
@@ -6609,10 +6606,10 @@
         <v>3</v>
       </c>
       <c r="J60" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y60" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z60" s="2">
         <v>0.5</v>
@@ -6648,7 +6645,7 @@
         <v>0</v>
       </c>
       <c r="AL60" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM60" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6679,7 +6676,7 @@
         <v>19</v>
       </c>
       <c r="B61" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C61">
         <v>500</v>
@@ -6703,7 +6700,7 @@
         <v>3</v>
       </c>
       <c r="Y61" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z61" s="2">
         <v>0.27</v>
@@ -6739,7 +6736,7 @@
         <v>0</v>
       </c>
       <c r="AL61" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM61" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6770,7 +6767,7 @@
         <v>81</v>
       </c>
       <c r="B62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C62">
         <v>300</v>
@@ -6794,10 +6791,10 @@
         <v>3</v>
       </c>
       <c r="J62" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N62" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z62" s="2">
         <v>0.2</v>
@@ -6832,8 +6829,13 @@
       <c r="AJ62" t="s">
         <v>0</v>
       </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Boss for ID10</t>
+        </is>
+      </c>
       <c r="AL62" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM62" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6864,7 +6866,7 @@
         <v>41</v>
       </c>
       <c r="B63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C63">
         <v>333</v>
@@ -6888,10 +6890,10 @@
         <v>3</v>
       </c>
       <c r="T63" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y63" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z63" s="2">
         <v>0.8</v>
@@ -6927,7 +6929,7 @@
         <v>0</v>
       </c>
       <c r="AL63" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM63" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6958,7 +6960,7 @@
         <v>84</v>
       </c>
       <c r="B64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C64">
         <v>200</v>
@@ -6982,7 +6984,7 @@
         <v>6</v>
       </c>
       <c r="O64" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z64" s="2">
         <v>0.9</v>
@@ -7017,8 +7019,13 @@
       <c r="AJ64" t="s">
         <v>0</v>
       </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Boss for ID23</t>
+        </is>
+      </c>
       <c r="AL64" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM64" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -7049,7 +7056,7 @@
         <v>35</v>
       </c>
       <c r="B65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C65">
         <v>200</v>
@@ -7073,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="J65" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z65" s="2">
         <v>0.27</v>
@@ -7109,7 +7116,7 @@
         <v>0</v>
       </c>
       <c r="AL65" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM65" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -7164,7 +7171,7 @@
         <v>6</v>
       </c>
       <c r="J66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z66" s="2">
         <v>1</v>
@@ -7200,7 +7207,7 @@
         <v>0</v>
       </c>
       <c r="AL66" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM66" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -7231,7 +7238,7 @@
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C67">
         <v>300</v>
@@ -7255,10 +7262,10 @@
         <v>3</v>
       </c>
       <c r="L67" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y67" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z67" s="2">
         <v>0.05</v>
@@ -7294,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="AL67" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM67" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -7349,10 +7356,10 @@
         <v>14</v>
       </c>
       <c r="J68" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K68" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z68" s="2">
         <v>0.1</v>
@@ -7388,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="AL68" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM68" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -7443,7 +7450,7 @@
         <v>3</v>
       </c>
       <c r="P69" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z69" s="2">
         <v>0.6</v>
@@ -7479,10 +7486,10 @@
         <v>0</v>
       </c>
       <c r="AK69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AL69" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AM69" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -7513,7 +7520,7 @@
         <v>86</v>
       </c>
       <c r="B70" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C70">
         <v>500</v>
@@ -7537,10 +7544,10 @@
         <v>6</v>
       </c>
       <c r="J70" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K70" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z70" s="2">
         <v>0.5</v>
@@ -7575,8 +7582,13 @@
       <c r="AJ70" t="s">
         <v>0</v>
       </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Boss for ID59</t>
+        </is>
+      </c>
       <c r="AL70" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM70" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -7607,7 +7619,7 @@
         <v>13</v>
       </c>
       <c r="B71" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C71">
         <v>500</v>
@@ -7631,10 +7643,10 @@
         <v>3</v>
       </c>
       <c r="O71" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y71" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z71" s="2">
         <v>0.3</v>
@@ -7670,7 +7682,7 @@
         <v>0</v>
       </c>
       <c r="AL71" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM71" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -7701,7 +7713,7 @@
         <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C72">
         <v>500</v>
@@ -7725,10 +7737,10 @@
         <v>3</v>
       </c>
       <c r="T72" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y72" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z72" s="2">
         <v>0</v>
@@ -7764,7 +7776,7 @@
         <v>0</v>
       </c>
       <c r="AL72" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM72" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -7795,7 +7807,7 @@
         <v>3</v>
       </c>
       <c r="B73" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C73">
         <v>375</v>
@@ -7819,13 +7831,13 @@
         <v>3</v>
       </c>
       <c r="J73" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q73" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y73" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z73" s="2">
         <v>0.5</v>
@@ -7861,7 +7873,7 @@
         <v>0</v>
       </c>
       <c r="AL73" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM73" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -7892,7 +7904,7 @@
         <v>21</v>
       </c>
       <c r="B74" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C74">
         <v>400</v>
@@ -7913,16 +7925,16 @@
         <v>100</v>
       </c>
       <c r="I74" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K74" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L74" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y74" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z74" s="2">
         <v>0.2</v>
@@ -7952,13 +7964,13 @@
         <v>3.5</v>
       </c>
       <c r="AI74" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AJ74" t="s">
         <v>0</v>
       </c>
       <c r="AL74" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM74" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -8019,7 +8031,7 @@
         <v>0.2</v>
       </c>
       <c r="Y75" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z75" s="2">
         <v>0.1</v>
@@ -8055,7 +8067,7 @@
         <v>18</v>
       </c>
       <c r="AL75" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AM75" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -8110,10 +8122,10 @@
         <v>3</v>
       </c>
       <c r="P76" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y76" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z76" s="2">
         <v>0.2</v>
@@ -8149,7 +8161,7 @@
         <v>0</v>
       </c>
       <c r="AL76" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM76" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -8180,7 +8192,7 @@
         <v>22</v>
       </c>
       <c r="B77" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C77">
         <v>400</v>
@@ -8204,7 +8216,7 @@
         <v>6</v>
       </c>
       <c r="J77" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z77" s="2">
         <v>0.33</v>
@@ -8240,7 +8252,7 @@
         <v>0</v>
       </c>
       <c r="AL77" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM77" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -8295,7 +8307,7 @@
         <v>3</v>
       </c>
       <c r="Y78" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z78" s="2">
         <v>0.2</v>
@@ -8331,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="AL78" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM78" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -8386,7 +8398,7 @@
         <v>3</v>
       </c>
       <c r="N79" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z79" s="2">
         <v>0.9</v>
@@ -8422,7 +8434,7 @@
         <v>0</v>
       </c>
       <c r="AL79" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM79" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -8477,7 +8489,7 @@
         <v>3</v>
       </c>
       <c r="O80" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z80" s="2">
         <v>0.8</v>
@@ -8512,8 +8524,13 @@
       <c r="AJ80" t="s">
         <v>0</v>
       </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Boss for ID13</t>
+        </is>
+      </c>
       <c r="AL80" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AM80" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -8568,7 +8585,7 @@
         <v>16</v>
       </c>
       <c r="J81" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z81" s="2">
         <v>0.25</v>
@@ -8604,7 +8621,7 @@
         <v>0</v>
       </c>
       <c r="AL81" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM81" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -8691,11 +8708,13 @@
       <c r="AJ82" t="s">
         <v>0</v>
       </c>
-      <c r="AK82" t="s">
-        <v>123</v>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Boss for ID36</t>
+        </is>
       </c>
       <c r="AL82" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM82" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -8789,10 +8808,10 @@
         <v>18</v>
       </c>
       <c r="AK83" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AL83" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AM83" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -8847,13 +8866,13 @@
         <v>6</v>
       </c>
       <c r="J84" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R84" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S84" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z84" s="2">
         <v>0.8</v>
@@ -8889,7 +8908,7 @@
         <v>0</v>
       </c>
       <c r="AL84" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AM84" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -8944,7 +8963,7 @@
         <v>14</v>
       </c>
       <c r="J85" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z85" s="2">
         <v>0.5</v>
@@ -8980,10 +8999,10 @@
         <v>0</v>
       </c>
       <c r="AK85" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AL85" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM85" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -9038,7 +9057,7 @@
         <v>3</v>
       </c>
       <c r="S86" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z86" s="2">
         <v>1</v>
@@ -9074,7 +9093,7 @@
         <v>0</v>
       </c>
       <c r="AL86" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM86" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -9129,10 +9148,10 @@
         <v>3</v>
       </c>
       <c r="T87" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y87" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z87" s="2">
         <v>0.2</v>
@@ -9168,7 +9187,7 @@
         <v>0</v>
       </c>
       <c r="AL87" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM87" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -9223,7 +9242,7 @@
         <v>6</v>
       </c>
       <c r="U88" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z88" s="2">
         <v>0.33</v>
@@ -9259,7 +9278,7 @@
         <v>0</v>
       </c>
       <c r="AL88" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM88" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -9314,10 +9333,10 @@
         <v>3</v>
       </c>
       <c r="Q89" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y89" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z89" s="2">
         <v>0.27</v>
@@ -9353,7 +9372,7 @@
         <v>0</v>
       </c>
       <c r="AL89" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM89" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -9408,10 +9427,10 @@
         <v>3</v>
       </c>
       <c r="T90" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y90" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z90" s="2">
         <v>0.15</v>
@@ -9447,7 +9466,7 @@
         <v>0</v>
       </c>
       <c r="AL90" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM90" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -9535,10 +9554,10 @@
         <v>0</v>
       </c>
       <c r="AK91" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AL91" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM91" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -9593,7 +9612,7 @@
         <v>3</v>
       </c>
       <c r="L92" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z92" s="2">
         <v>0.1</v>
@@ -9629,7 +9648,7 @@
         <v>0</v>
       </c>
       <c r="AL92" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM92" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -9692,21 +9711,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" t="s">
         <v>152</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>153</v>
-      </c>
-      <c r="C1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s">
         <v>150</v>
-      </c>
-      <c r="B2" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -9728,7 +9747,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/docs/RPG_0.1.xlsx
+++ b/docs/RPG_0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sonstiges\3D RPG\game\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A84110-B90B-44D4-85F2-33B9373C8591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB53BD8-E3BB-4CD1-BDA9-EA67D40E6557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9345" yWindow="3465" windowWidth="28800" windowHeight="11235" xr2:uid="{4BE2A854-3C52-4E67-A093-93255C02F786}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{4BE2A854-3C52-4E67-A093-93255C02F786}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="165">
   <si>
     <t>False</t>
   </si>
@@ -558,6 +558,18 @@
   <si>
     <t>entity 4:
 no_of_attacks (Melee only)</t>
+  </si>
+  <si>
+    <t>Boss for ID10</t>
+  </si>
+  <si>
+    <t>Boss for ID23</t>
+  </si>
+  <si>
+    <t>Boss for ID59</t>
+  </si>
+  <si>
+    <t>Boss for ID36</t>
   </si>
 </sst>
 </file>
@@ -644,10 +656,17 @@
   </cellStyles>
   <dxfs count="10">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
@@ -671,13 +690,6 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -692,21 +704,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D90D8A91-E0CE-4C15-A63B-1C55C33A6140}" name="_csv247" displayName="_csv247" ref="A1:AN92" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D90D8A91-E0CE-4C15-A63B-1C55C33A6140}" name="_csv247" displayName="_csv247" ref="A1:AN92" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="A1:AN92" xr:uid="{4F99A048-8AA6-4189-B2E2-F108A96BB99C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AN92">
     <sortCondition ref="AM1:AM92"/>
   </sortState>
   <tableColumns count="40">
-    <tableColumn id="1" xr3:uid="{881067C4-F102-4BAF-8FEB-F081B637E7C9}" name="ID" dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{5CB2E5FB-D646-4A47-B48A-48F4E900E944}" name="entity 0:_x000a_name" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{881067C4-F102-4BAF-8FEB-F081B637E7C9}" name="ID" dataDxfId="8"/>
+    <tableColumn id="21" xr3:uid="{5CB2E5FB-D646-4A47-B48A-48F4E900E944}" name="entity 0:_x000a_name" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{B3453128-B92B-4DFE-A3A7-0792C25E7A14}" name="entity 1:_x000a_health"/>
     <tableColumn id="3" xr3:uid="{E0F364BE-C9D7-421D-8D53-CCF2EE2C58E0}" name="entity 2:_x000a_armor"/>
     <tableColumn id="4" xr3:uid="{661EC57C-D67C-4DE9-9867-BFD0620183A3}" name="entity 3:_x000a_speed"/>
     <tableColumn id="5" xr3:uid="{F552EB56-3980-4FA8-B694-808465E6DD8A}" name="entity 4:_x000a_no_of_attacks (Melee only)"/>
     <tableColumn id="22" xr3:uid="{0487C91F-9C2F-4E75-892B-F0DCAB8F7E1A}" name="entity 5:_x000a_damage_min"/>
     <tableColumn id="23" xr3:uid="{A62A4E70-3628-41B1-8FE3-377B36336BF4}" name="entity 6:_x000a_damage_max"/>
-    <tableColumn id="8" xr3:uid="{B2A15422-B7F1-4B55-BD0E-2C4DDBFFC1ED}" name="entity 7:_x000a_attack_type" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{B2A15422-B7F1-4B55-BD0E-2C4DDBFFC1ED}" name="entity 7:_x000a_attack_type" dataDxfId="6"/>
     <tableColumn id="26" xr3:uid="{574C8C33-5E35-4BB7-B93B-BCCC4F5A8F24}" name="entity 8a: _x000a_ranged attack"/>
     <tableColumn id="29" xr3:uid="{C620C28C-7B65-4C2A-A955-6EF0FC88408A}" name="entity 8b: _x000a_hits_all_characters_at_once"/>
     <tableColumn id="28" xr3:uid="{67DC7C28-804E-4553-A851-3EB02D5073BD}" name="entity 8c: _x000a_causes_status_poisoned"/>
@@ -722,16 +734,16 @@
     <tableColumn id="39" xr3:uid="{FE9BCC63-A58F-4EE4-AEF0-714F5229CD56}" name="entity 8l: _x000a_regeneration_per_turn_in_percent_of total_life"/>
     <tableColumn id="40" xr3:uid="{20EFEFED-5BC7-4680-8D94-F0FFDF66C696}" name="entity 8m: _x000a_steal_mana_on_hit_in_percent_of_characters_max_mana"/>
     <tableColumn id="41" xr3:uid="{6B83D3CE-7E9F-4FEC-A9B7-E09FF7C7DABE}" name="entity 8n: _x000a_increases_magical_age_by_1_year_on_hit"/>
-    <tableColumn id="10" xr3:uid="{657AB867-1E43-41EC-95BE-4DF86DC71643}" name="entity 9:_x000a_outside_spawner_hut_xp" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{657AB867-1E43-41EC-95BE-4DF86DC71643}" name="entity 9:_x000a_outside_spawner_hut_xp" dataDxfId="5"/>
     <tableColumn id="11" xr3:uid="{C864C4B0-6F86-4266-84B7-0009F0740F0B}" name="entity 10:_x000a_res_magic"/>
     <tableColumn id="12" xr3:uid="{4DE80521-738A-490D-8660-B2E4BE035E51}" name="entity 11:_x000a_res_fire"/>
     <tableColumn id="13" xr3:uid="{FEFD4387-19A1-41A1-9279-3622879EEEF7}" name="entity 12:_x000a_res_physical"/>
     <tableColumn id="15" xr3:uid="{9D486DD9-3A76-4B9D-A48E-45B8AC5A9204}" name="entity 13:_x000a_res_cold"/>
     <tableColumn id="16" xr3:uid="{674684F8-3D91-4BFB-A915-BAFCD2C82B25}" name="entity 14:_x000a_res_poison"/>
     <tableColumn id="18" xr3:uid="{4F25CA0D-398A-4ADE-B1B4-5F0BB7C038DA}" name="entity 15:_x000a_exp_old (not used anymore)"/>
-    <tableColumn id="27" xr3:uid="{BB0197D4-3C5C-4D64-BB3F-0966359DE0DF}" name="entity 16:_x000a_gold" dataDxfId="3"/>
+    <tableColumn id="27" xr3:uid="{BB0197D4-3C5C-4D64-BB3F-0966359DE0DF}" name="entity 16:_x000a_gold" dataDxfId="4"/>
     <tableColumn id="25" xr3:uid="{ED29C8D4-1AB4-48DC-AD5F-5B5BCA75AC90}" name="entity 17:_x000a_treasure_level_old (not used anymore)"/>
-    <tableColumn id="6" xr3:uid="{306F37DE-3F0E-4874-9CA6-CA8E4537DAC0}" name="entity 18:_x000a_icon_height" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{306F37DE-3F0E-4874-9CA6-CA8E4537DAC0}" name="entity 18:_x000a_icon_height" dataDxfId="3"/>
     <tableColumn id="7" xr3:uid="{06CC750E-0BC9-4044-ADAB-702E10B69198}" name="entity 19:_x000a_terrain"/>
     <tableColumn id="14" xr3:uid="{10A0D880-46D4-4EF1-9E97-94B8F7FF7F8A}" name="entity 20:_x000a_undead"/>
     <tableColumn id="17" xr3:uid="{5C125C46-427D-41B4-A8E2-C627B813F7BF}" name="entity 21:_x000a_final_boss"/>
@@ -742,7 +754,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -755,7 +767,7 @@
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{8A88862A-3CB6-4053-9301-EB3CFDFFA903}" name="entity 24: treasure_level_new" dataDxfId="0"/>
+    <tableColumn id="20" xr3:uid="{8A88862A-3CB6-4053-9301-EB3CFDFFA903}" name="entity 24: treasure_level_new" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1285,7 +1297,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -1380,7 +1392,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -1431,7 +1443,7 @@
       </c>
       <c r="Y4" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>9360</v>
+        <v>6110</v>
       </c>
       <c r="Z4" s="2">
         <v>0</v>
@@ -1475,7 +1487,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -1487,7 +1499,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>720</v>
+        <v>470</v>
       </c>
       <c r="AN4">
         <v>1</v>
@@ -1526,7 +1538,7 @@
       </c>
       <c r="Y5" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>13162.5</v>
+        <v>7475</v>
       </c>
       <c r="Z5" s="2">
         <v>0.25</v>
@@ -1570,7 +1582,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -1582,7 +1594,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>1012.5</v>
+        <v>575</v>
       </c>
       <c r="AN5">
         <v>1</v>
@@ -1661,7 +1673,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -1673,7 +1685,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>1840</v>
+        <v>1046</v>
       </c>
       <c r="AN6">
         <v>1</v>
@@ -1712,7 +1724,7 @@
       </c>
       <c r="Y7" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>29783</v>
+        <v>16354</v>
       </c>
       <c r="Z7" s="2">
         <v>0.33</v>
@@ -1756,7 +1768,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -1768,7 +1780,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>2291</v>
+        <v>1258</v>
       </c>
       <c r="AN7">
         <v>1</v>
@@ -1850,7 +1862,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -1862,7 +1874,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>2802</v>
+        <v>1472</v>
       </c>
       <c r="AN8">
         <v>1</v>
@@ -1901,7 +1913,7 @@
       </c>
       <c r="Y9" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>42809</v>
+        <v>22756.5</v>
       </c>
       <c r="Z9" s="2">
         <v>0.17</v>
@@ -1945,7 +1957,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -1957,7 +1969,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>3293</v>
+        <v>1750.5</v>
       </c>
       <c r="AN9">
         <v>1</v>
@@ -2039,7 +2051,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -2051,7 +2063,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>4220</v>
+        <v>2220</v>
       </c>
       <c r="AN10">
         <v>1</v>
@@ -2127,7 +2139,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -2139,7 +2151,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>4288</v>
+        <v>2288</v>
       </c>
       <c r="AN11">
         <v>1</v>
@@ -2178,7 +2190,7 @@
       </c>
       <c r="Y12" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>61087</v>
+        <v>32129.5</v>
       </c>
       <c r="Z12" s="2">
         <v>0.6</v>
@@ -2222,7 +2234,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -2234,7 +2246,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>4699</v>
+        <v>2471.5</v>
       </c>
       <c r="AN12">
         <v>1</v>
@@ -2316,7 +2328,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -2328,7 +2340,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>5275</v>
+        <v>2725</v>
       </c>
       <c r="AN13">
         <v>1</v>
@@ -2407,7 +2419,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -2419,7 +2431,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>5325</v>
+        <v>2775</v>
       </c>
       <c r="AN14">
         <v>1</v>
@@ -2458,7 +2470,7 @@
       </c>
       <c r="Y15" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>90610</v>
+        <v>47710</v>
       </c>
       <c r="Z15" s="2">
         <v>0.25</v>
@@ -2502,7 +2514,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -2514,7 +2526,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>6970</v>
+        <v>3670</v>
       </c>
       <c r="AN15">
         <v>1</v>
@@ -2550,7 +2562,7 @@
       </c>
       <c r="Y16" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>108940</v>
+        <v>57980</v>
       </c>
       <c r="Z16" s="2">
         <v>0.2</v>
@@ -2594,7 +2606,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -2606,7 +2618,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>8380</v>
+        <v>4460</v>
       </c>
       <c r="AN16">
         <v>1</v>
@@ -2691,7 +2703,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -2703,7 +2715,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>8860</v>
+        <v>4610</v>
       </c>
       <c r="AN17">
         <v>1</v>
@@ -2785,7 +2797,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -2797,7 +2809,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>9058</v>
+        <v>4627</v>
       </c>
       <c r="AN18">
         <v>1</v>
@@ -2836,7 +2848,7 @@
       </c>
       <c r="Y19" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>132314</v>
+        <v>73307</v>
       </c>
       <c r="Z19" s="2">
         <v>0.33</v>
@@ -2880,7 +2892,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -2892,7 +2904,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>10178</v>
+        <v>5639</v>
       </c>
       <c r="AN19">
         <v>1</v>
@@ -2931,7 +2943,7 @@
       </c>
       <c r="Y20" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>172380</v>
+        <v>91130</v>
       </c>
       <c r="Z20" s="2">
         <v>0.5</v>
@@ -2975,7 +2987,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -2987,7 +2999,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>13260</v>
+        <v>7010</v>
       </c>
       <c r="AN20">
         <v>2</v>
@@ -3026,7 +3038,7 @@
       </c>
       <c r="Y21" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>177775</v>
+        <v>91195</v>
       </c>
       <c r="Z21" s="2">
         <v>0.1</v>
@@ -3070,7 +3082,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -3082,7 +3094,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>13675</v>
+        <v>7015</v>
       </c>
       <c r="AN21">
         <v>2</v>
@@ -3164,7 +3176,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -3176,7 +3188,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>14708</v>
+        <v>7608</v>
       </c>
       <c r="AN22">
         <v>2</v>
@@ -3184,56 +3196,58 @@
     </row>
     <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C23">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D23">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E23">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
         <v>4</v>
       </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
       <c r="H23">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I23" t="s">
         <v>3</v>
       </c>
-      <c r="Y23" s="10">
-        <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>196885</v>
+      <c r="O23" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y23" s="10" t="s">
+        <v>133</v>
       </c>
       <c r="Z23" s="2">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AC23" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AD23" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="AF23">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="AG23">
         <v>1</v>
@@ -3256,7 +3270,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -3268,7 +3282,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>15145</v>
+        <v>7792</v>
       </c>
       <c r="AN23">
         <v>2</v>
@@ -3276,58 +3290,56 @@
     </row>
     <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C24">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H24">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I24" t="s">
         <v>3</v>
       </c>
-      <c r="O24" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y24" s="10" t="s">
-        <v>133</v>
+      <c r="Y24" s="10">
+        <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
+        <v>102992.5</v>
       </c>
       <c r="Z24" s="2">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AA24" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AB24" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AC24" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AD24" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AE24">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="AF24">
-        <v>250</v>
+        <v>30</v>
       </c>
       <c r="AG24">
         <v>1</v>
@@ -3350,7 +3362,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -3362,7 +3374,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>15292</v>
+        <v>7922.5</v>
       </c>
       <c r="AN24">
         <v>2</v>
@@ -3441,7 +3453,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -3453,7 +3465,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>15892</v>
+        <v>8242</v>
       </c>
       <c r="AN25">
         <v>2</v>
@@ -3492,7 +3504,7 @@
       </c>
       <c r="Y26" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>210106</v>
+        <v>108706</v>
       </c>
       <c r="Z26" s="2">
         <v>0.6</v>
@@ -3536,7 +3548,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -3548,7 +3560,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>16162</v>
+        <v>8362</v>
       </c>
       <c r="AN26">
         <v>2</v>
@@ -3556,55 +3568,55 @@
     </row>
     <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C27">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E27">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I27" t="s">
         <v>3</v>
       </c>
-      <c r="Y27" s="10" t="s">
+      <c r="N27" t="s">
         <v>133</v>
       </c>
       <c r="Z27" s="2">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="AA27" s="2">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AB27" s="2">
         <v>0</v>
       </c>
       <c r="AC27" s="2">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AD27" s="2">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AE27">
         <v>4000</v>
       </c>
       <c r="AF27">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="AG27">
         <v>2</v>
@@ -3619,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="AL27" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AM27" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3627,7 +3639,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -3639,7 +3651,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>16260</v>
+        <v>8450</v>
       </c>
       <c r="AN27">
         <v>2</v>
@@ -3647,55 +3659,55 @@
     </row>
     <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28">
+        <v>18</v>
+      </c>
+      <c r="B28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28">
+        <v>70</v>
+      </c>
+      <c r="D28">
         <v>10</v>
       </c>
-      <c r="B28" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28">
-        <v>50</v>
-      </c>
-      <c r="D28">
+      <c r="E28">
+        <v>18</v>
+      </c>
+      <c r="F28">
+        <v>6</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28">
         <v>15</v>
       </c>
-      <c r="E28">
-        <v>25</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28">
-        <v>2</v>
-      </c>
-      <c r="H28">
-        <v>30</v>
-      </c>
       <c r="I28" t="s">
         <v>3</v>
       </c>
-      <c r="N28" t="s">
+      <c r="Y28" s="10" t="s">
         <v>133</v>
       </c>
       <c r="Z28" s="2">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="AA28" s="2">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AB28" s="2">
         <v>0</v>
       </c>
       <c r="AC28" s="2">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AD28" s="2">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE28">
         <v>4000</v>
       </c>
       <c r="AF28">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="AG28">
         <v>2</v>
@@ -3710,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="AL28" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AM28" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3718,7 +3730,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -3730,7 +3742,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>16400</v>
+        <v>8616</v>
       </c>
       <c r="AN28">
         <v>2</v>
@@ -3738,70 +3750,70 @@
     </row>
     <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C29">
+        <v>40</v>
+      </c>
+      <c r="D29">
+        <v>20</v>
+      </c>
+      <c r="E29">
+        <v>30</v>
+      </c>
+      <c r="F29">
+        <v>8</v>
+      </c>
+      <c r="G29">
+        <v>3</v>
+      </c>
+      <c r="H29">
+        <v>9</v>
+      </c>
+      <c r="I29" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y29" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>10000</v>
+      </c>
+      <c r="AF29">
         <v>50</v>
       </c>
-      <c r="D29">
-        <v>12</v>
-      </c>
-      <c r="E29">
-        <v>20</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <v>4</v>
-      </c>
-      <c r="H29">
-        <v>16</v>
-      </c>
-      <c r="I29" t="s">
-        <v>6</v>
-      </c>
-      <c r="X29" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z29" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="AA29" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>16000</v>
-      </c>
-      <c r="AF29">
-        <v>150</v>
-      </c>
       <c r="AG29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH29" s="1">
         <v>3.5</v>
       </c>
       <c r="AI29" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AJ29" t="s">
         <v>0</v>
       </c>
       <c r="AL29" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AM29" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3809,7 +3821,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -3821,7 +3833,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>16400</v>
+        <v>9440</v>
       </c>
       <c r="AN29">
         <v>2</v>
@@ -3829,37 +3841,37 @@
     </row>
     <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C30">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D30">
+        <v>12</v>
+      </c>
+      <c r="E30">
         <v>20</v>
       </c>
-      <c r="E30">
-        <v>30</v>
-      </c>
       <c r="F30">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I30" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y30" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="X30" t="s">
         <v>133</v>
       </c>
       <c r="Z30" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AA30" s="2">
         <v>0</v>
@@ -3874,25 +3886,25 @@
         <v>0</v>
       </c>
       <c r="AE30">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="AF30">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH30" s="1">
         <v>3.5</v>
       </c>
       <c r="AI30" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AJ30" t="s">
         <v>0</v>
       </c>
       <c r="AL30" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AM30" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -3900,7 +3912,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -3912,7 +3924,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>17440</v>
+        <v>10300</v>
       </c>
       <c r="AN30">
         <v>2</v>
@@ -3948,7 +3960,7 @@
       </c>
       <c r="Y31" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>280436</v>
+        <v>143936</v>
       </c>
       <c r="Z31" s="2">
         <v>1</v>
@@ -3992,7 +4004,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -4004,7 +4016,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>21572</v>
+        <v>11072</v>
       </c>
       <c r="AN31">
         <v>2</v>
@@ -4086,7 +4098,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -4098,7 +4110,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>21920</v>
+        <v>11250</v>
       </c>
       <c r="AN32">
         <v>2</v>
@@ -4174,7 +4186,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -4186,7 +4198,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>22600</v>
+        <v>12200</v>
       </c>
       <c r="AN33">
         <v>2</v>
@@ -4265,7 +4277,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -4277,7 +4289,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>23860</v>
+        <v>12860</v>
       </c>
       <c r="AN34">
         <v>2</v>
@@ -4356,7 +4368,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -4368,7 +4380,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>25864</v>
+        <v>13364</v>
       </c>
       <c r="AN35">
         <v>2</v>
@@ -4444,7 +4456,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -4456,7 +4468,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>26885</v>
+        <v>14072.5</v>
       </c>
       <c r="AN36">
         <v>2</v>
@@ -4495,7 +4507,7 @@
       </c>
       <c r="Y37" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>420836</v>
+        <v>215436</v>
       </c>
       <c r="Z37" s="2">
         <v>0</v>
@@ -4539,7 +4551,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -4551,7 +4563,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>32372</v>
+        <v>16572</v>
       </c>
       <c r="AN37">
         <v>2</v>
@@ -4559,43 +4571,43 @@
     </row>
     <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C38">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D38">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E38">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H38">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I38" t="s">
-        <v>6</v>
-      </c>
-      <c r="X38" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y38" s="10" t="s">
         <v>133</v>
       </c>
       <c r="Z38" s="2">
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="AA38" s="2">
         <v>0</v>
       </c>
       <c r="AB38" s="2">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AC38" s="2">
         <v>0</v>
@@ -4604,13 +4616,13 @@
         <v>0</v>
       </c>
       <c r="AE38">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="AF38">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="AG38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH38" s="1">
         <v>3.5</v>
@@ -4619,10 +4631,10 @@
         <v>1</v>
       </c>
       <c r="AJ38" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AM38" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -4630,7 +4642,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -4642,7 +4654,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>33675</v>
+        <v>17562</v>
       </c>
       <c r="AN38">
         <v>3</v>
@@ -4650,25 +4662,25 @@
     </row>
     <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C39">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D39">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E39">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F39">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H39">
         <v>30</v>
@@ -4676,26 +4688,33 @@
       <c r="I39" t="s">
         <v>3</v>
       </c>
+      <c r="J39" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y39" s="10">
+        <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
+        <v>235950</v>
+      </c>
       <c r="Z39" s="2">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AA39" s="2">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="AB39" s="2">
         <v>0</v>
       </c>
       <c r="AC39" s="2">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="AD39" s="2">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="AE39">
         <v>20000</v>
       </c>
       <c r="AF39">
-        <v>500</v>
+        <v>2400</v>
       </c>
       <c r="AG39">
         <v>3</v>
@@ -4718,7 +4737,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -4730,7 +4749,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>33690</v>
+        <v>18150</v>
       </c>
       <c r="AN39">
         <v>3</v>
@@ -4738,25 +4757,25 @@
     </row>
     <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C40">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D40">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E40">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H40">
         <v>30</v>
@@ -4764,33 +4783,26 @@
       <c r="I40" t="s">
         <v>3</v>
       </c>
-      <c r="J40" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y40" s="10">
-        <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>438750</v>
-      </c>
       <c r="Z40" s="2">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="AA40" s="2">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="AB40" s="2">
         <v>0</v>
       </c>
       <c r="AC40" s="2">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="AD40" s="2">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="AE40">
         <v>20000</v>
       </c>
       <c r="AF40">
-        <v>2400</v>
+        <v>500</v>
       </c>
       <c r="AG40">
         <v>3</v>
@@ -4813,7 +4825,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -4825,7 +4837,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>33750</v>
+        <v>18165</v>
       </c>
       <c r="AN40">
         <v>3</v>
@@ -4833,43 +4845,43 @@
     </row>
     <row r="41" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C41">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E41">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H41">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I41" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Y41" s="10" t="s">
         <v>133</v>
       </c>
       <c r="Z41" s="2">
-        <v>0.9</v>
+        <v>0.27</v>
       </c>
       <c r="AA41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB41" s="2">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AC41" s="2">
         <v>0</v>
@@ -4878,10 +4890,10 @@
         <v>0</v>
       </c>
       <c r="AE41">
-        <v>16000</v>
+        <v>30000</v>
       </c>
       <c r="AF41">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AG41">
         <v>3</v>
@@ -4896,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="AL41" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AM41" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -4904,7 +4916,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -4916,7 +4928,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>34812</v>
+        <v>18682.5</v>
       </c>
       <c r="AN41">
         <v>3</v>
@@ -4924,55 +4936,58 @@
     </row>
     <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C42">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="D42">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E42">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I42" t="s">
         <v>14</v>
       </c>
+      <c r="J42" t="s">
+        <v>133</v>
+      </c>
       <c r="Y42" s="10" t="s">
         <v>133</v>
       </c>
       <c r="Z42" s="2">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="AA42" s="2">
         <v>1</v>
       </c>
       <c r="AB42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC42" s="2">
         <v>0</v>
       </c>
       <c r="AD42" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE42">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="AF42">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AG42">
         <v>3</v>
@@ -4987,7 +5002,7 @@
         <v>0</v>
       </c>
       <c r="AL42" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM42" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -4995,7 +5010,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -5007,7 +5022,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>35385</v>
+        <v>18985</v>
       </c>
       <c r="AN42">
         <v>3</v>
@@ -5015,61 +5030,58 @@
     </row>
     <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43">
+        <v>28</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43">
+        <v>100</v>
+      </c>
+      <c r="D43">
+        <v>13</v>
+      </c>
+      <c r="E43">
         <v>25</v>
       </c>
-      <c r="B43" t="s">
-        <v>59</v>
-      </c>
-      <c r="C43">
-        <v>150</v>
-      </c>
-      <c r="D43">
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
         <v>10</v>
       </c>
-      <c r="E43">
-        <v>30</v>
-      </c>
-      <c r="F43">
-        <v>2</v>
-      </c>
-      <c r="G43">
-        <v>2</v>
-      </c>
       <c r="H43">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J43" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y43" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="X43" t="s">
         <v>133</v>
       </c>
       <c r="Z43" s="2">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="AA43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC43" s="2">
         <v>0</v>
       </c>
       <c r="AD43" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>25000</v>
+        <v>32000</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AG43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH43" s="1">
         <v>3.5</v>
@@ -5078,10 +5090,10 @@
         <v>1</v>
       </c>
       <c r="AJ43" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL43" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AM43" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5089,7 +5101,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -5101,7 +5113,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>36310</v>
+        <v>19525</v>
       </c>
       <c r="AN43">
         <v>3</v>
@@ -5140,7 +5152,7 @@
       </c>
       <c r="Y44" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>544440</v>
+        <v>278330</v>
       </c>
       <c r="Z44" s="2">
         <v>7.0000000000000007E-2</v>
@@ -5184,7 +5196,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -5196,7 +5208,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>41880</v>
+        <v>21410</v>
       </c>
       <c r="AN44">
         <v>3</v>
@@ -5204,41 +5216,41 @@
     </row>
     <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C45">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="D45">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E45">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H45">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I45" t="s">
         <v>3</v>
       </c>
-      <c r="V45">
-        <v>0.05</v>
+      <c r="P45" t="s">
+        <v>133</v>
       </c>
       <c r="Y45" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>575900</v>
+        <v>306280</v>
       </c>
       <c r="Z45" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AA45" s="2">
         <v>0</v>
@@ -5247,19 +5259,19 @@
         <v>0</v>
       </c>
       <c r="AC45" s="2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AD45" s="2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AE45">
-        <v>50000</v>
+        <v>16000</v>
       </c>
       <c r="AF45">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="AG45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH45" s="1">
         <v>3.5</v>
@@ -5271,7 +5283,7 @@
         <v>0</v>
       </c>
       <c r="AL45" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AM45" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5279,7 +5291,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -5291,7 +5303,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>44300</v>
+        <v>23560</v>
       </c>
       <c r="AN45">
         <v>3</v>
@@ -5299,19 +5311,19 @@
     </row>
     <row r="46" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C46">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D46">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E46">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -5320,23 +5332,23 @@
         <v>4</v>
       </c>
       <c r="H46">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="I46" t="s">
         <v>6</v>
       </c>
-      <c r="W46">
-        <v>0.5</v>
+      <c r="J46" t="s">
+        <v>133</v>
       </c>
       <c r="Z46" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AA46" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="2">
         <v>0.9</v>
       </c>
-      <c r="AA46" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="2">
-        <v>0</v>
-      </c>
       <c r="AC46" s="2">
         <v>0</v>
       </c>
@@ -5344,13 +5356,13 @@
         <v>0</v>
       </c>
       <c r="AE46">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="AF46">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="AG46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH46" s="1">
         <v>3.5</v>
@@ -5359,10 +5371,10 @@
         <v>1</v>
       </c>
       <c r="AJ46" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL46" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AM46" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5370,7 +5382,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -5382,7 +5394,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>44300</v>
+        <v>25150</v>
       </c>
       <c r="AN46">
         <v>3</v>
@@ -5390,41 +5402,41 @@
     </row>
     <row r="47" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="B47" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C47">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D47">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E47">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="I47" t="s">
         <v>3</v>
       </c>
-      <c r="P47" t="s">
-        <v>133</v>
+      <c r="V47">
+        <v>0.05</v>
       </c>
       <c r="Y47" s="10">
         <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>583180</v>
+        <v>332150</v>
       </c>
       <c r="Z47" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" s="2">
         <v>0</v>
@@ -5433,19 +5445,19 @@
         <v>0</v>
       </c>
       <c r="AC47" s="2">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AD47" s="2">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AE47">
-        <v>16000</v>
+        <v>50000</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="AG47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH47" s="1">
         <v>3.5</v>
@@ -5457,7 +5469,7 @@
         <v>0</v>
       </c>
       <c r="AL47" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AM47" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5465,7 +5477,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -5477,7 +5489,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>44860</v>
+        <v>25550</v>
       </c>
       <c r="AN47">
         <v>3</v>
@@ -5485,13 +5497,13 @@
     </row>
     <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C48">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="D48">
         <v>15</v>
@@ -5500,25 +5512,26 @@
         <v>30</v>
       </c>
       <c r="F48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="I48" t="s">
         <v>3</v>
       </c>
-      <c r="T48" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y48" s="10" t="s">
-        <v>133</v>
+      <c r="J48" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y48" s="10">
+        <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
+        <v>345670</v>
       </c>
       <c r="Z48" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AA48" s="2">
         <v>0</v>
@@ -5533,10 +5546,10 @@
         <v>0</v>
       </c>
       <c r="AE48">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="AF48">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="AG48">
         <v>3</v>
@@ -5551,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="AL48" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AM48" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5559,7 +5572,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -5571,7 +5584,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>45630</v>
+        <v>26590</v>
       </c>
       <c r="AN48">
         <v>3</v>
@@ -5579,33 +5592,36 @@
     </row>
     <row r="49" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C49">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="D49">
         <v>15</v>
       </c>
       <c r="E49">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H49">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="I49" t="s">
-        <v>6</v>
-      </c>
-      <c r="J49" t="s">
+        <v>3</v>
+      </c>
+      <c r="T49" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y49" s="10" t="s">
         <v>133</v>
       </c>
       <c r="Z49" s="2">
@@ -5615,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="AB49" s="2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AC49" s="2">
         <v>0</v>
@@ -5624,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="AE49">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="AF49">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="AG49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH49" s="1">
         <v>3.5</v>
@@ -5639,10 +5655,10 @@
         <v>1</v>
       </c>
       <c r="AJ49" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AM49" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5650,7 +5666,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -5662,7 +5678,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>49150</v>
+        <v>26755</v>
       </c>
       <c r="AN49">
         <v>3</v>
@@ -5670,47 +5686,43 @@
     </row>
     <row r="50" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C50">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="D50">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E50">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50">
         <v>2</v>
       </c>
       <c r="H50">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="I50" t="s">
         <v>3</v>
       </c>
-      <c r="J50" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y50" s="10">
-        <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>686920</v>
+      <c r="O50" t="s">
+        <v>133</v>
       </c>
       <c r="Z50" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AA50" s="2">
         <v>0</v>
       </c>
       <c r="AB50" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AC50" s="2">
         <v>0</v>
@@ -5719,13 +5731,13 @@
         <v>0</v>
       </c>
       <c r="AE50">
-        <v>25000</v>
+        <v>40000</v>
       </c>
       <c r="AF50">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH50" s="1">
         <v>3.5</v>
@@ -5737,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="AL50" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AM50" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5745,7 +5757,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -5757,7 +5769,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>52840</v>
+        <v>28960</v>
       </c>
       <c r="AN50">
         <v>3</v>
@@ -5765,43 +5777,43 @@
     </row>
     <row r="51" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C51">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="D51">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E51">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F51">
         <v>4</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H51">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I51" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O51" t="s">
         <v>133</v>
       </c>
       <c r="Z51" s="2">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AA51" s="2">
         <v>0</v>
       </c>
       <c r="AB51" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AC51" s="2">
         <v>0</v>
@@ -5810,10 +5822,10 @@
         <v>0</v>
       </c>
       <c r="AE51">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AG51">
         <v>4</v>
@@ -5828,7 +5840,7 @@
         <v>0</v>
       </c>
       <c r="AL51" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AM51" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5836,7 +5848,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -5848,7 +5860,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>54460</v>
+        <v>33000</v>
       </c>
       <c r="AN51">
         <v>3</v>
@@ -5856,22 +5868,22 @@
     </row>
     <row r="52" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="B52" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C52">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D52">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E52">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G52">
         <v>50</v>
@@ -5880,16 +5892,20 @@
         <v>50</v>
       </c>
       <c r="I52" t="s">
-        <v>6</v>
-      </c>
-      <c r="O52" t="s">
-        <v>133</v>
+        <v>14</v>
+      </c>
+      <c r="J52" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y52" s="10">
+        <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
+        <v>436150</v>
       </c>
       <c r="Z52" s="2">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="AA52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB52" s="2">
         <v>0</v>
@@ -5898,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="AD52" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AE52">
-        <v>60000</v>
+        <v>18000</v>
       </c>
       <c r="AF52">
-        <v>300</v>
+        <v>3500</v>
       </c>
       <c r="AG52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH52" s="1">
         <v>3.5</v>
@@ -5919,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="AL52" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AM52" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -5927,7 +5943,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -5939,7 +5955,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>58900</v>
+        <v>33550</v>
       </c>
       <c r="AN52">
         <v>3</v>
@@ -5947,44 +5963,40 @@
     </row>
     <row r="53" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C53">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D53">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E53">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="H53">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="I53" t="s">
-        <v>14</v>
-      </c>
-      <c r="J53" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y53" s="10">
-        <f>_csv247[[#This Row],[entity 23: XP_new (While entity 24 give a rough idea of where place the monsters, the XP is the fine tuning. start with the lowest XP and use higher XP monsters, the further the heroes are venturing out)]]*13</f>
-        <v>851500</v>
+        <v>6</v>
+      </c>
+      <c r="W53">
+        <v>0.5</v>
       </c>
       <c r="Z53" s="2">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AA53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB53" s="2">
         <v>0</v>
@@ -5993,13 +6005,13 @@
         <v>0</v>
       </c>
       <c r="AD53" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AE53">
-        <v>18000</v>
+        <v>30000</v>
       </c>
       <c r="AF53">
-        <v>3500</v>
+        <v>250</v>
       </c>
       <c r="AG53">
         <v>3</v>
@@ -6014,7 +6026,7 @@
         <v>0</v>
       </c>
       <c r="AL53" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AM53" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6022,7 +6034,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -6034,7 +6046,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>65500</v>
+        <v>34850</v>
       </c>
       <c r="AN53">
         <v>3</v>
@@ -6042,58 +6054,58 @@
     </row>
     <row r="54" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C54">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D54">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E54">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54">
+        <v>4</v>
+      </c>
+      <c r="H54">
+        <v>60</v>
+      </c>
+      <c r="I54" t="s">
         <v>6</v>
       </c>
-      <c r="H54">
-        <v>120</v>
-      </c>
-      <c r="I54" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="2">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AA54" s="2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AB54" s="2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AC54" s="2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AD54" s="2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AE54">
-        <v>60000</v>
+        <v>120000</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>6450</v>
       </c>
       <c r="AG54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH54" s="1">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AI54" t="s">
         <v>1</v>
@@ -6102,7 +6114,7 @@
         <v>0</v>
       </c>
       <c r="AL54" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AM54" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6110,7 +6122,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -6122,7 +6134,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>81680</v>
+        <v>44020</v>
       </c>
       <c r="AN54">
         <v>3</v>
@@ -6130,58 +6142,58 @@
     </row>
     <row r="55" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C55">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D55">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E55">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55">
+        <v>6</v>
+      </c>
+      <c r="H55">
+        <v>120</v>
+      </c>
+      <c r="I55" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z55" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AC55" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE55">
+        <v>60000</v>
+      </c>
+      <c r="AF55">
+        <v>0</v>
+      </c>
+      <c r="AG55">
         <v>4</v>
       </c>
-      <c r="H55">
-        <v>60</v>
-      </c>
-      <c r="I55" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z55" s="2">
-        <v>0.17</v>
-      </c>
-      <c r="AA55" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="AB55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC55" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="AD55" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="AE55">
-        <v>120000</v>
-      </c>
-      <c r="AF55">
-        <v>6450</v>
-      </c>
-      <c r="AG55">
-        <v>5</v>
-      </c>
       <c r="AH55" s="1">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AI55" t="s">
         <v>1</v>
@@ -6190,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="AL55" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="AM55" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6198,7 +6210,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -6210,7 +6222,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>86760</v>
+        <v>45880</v>
       </c>
       <c r="AN55">
         <v>3</v>
@@ -6218,55 +6230,55 @@
     </row>
     <row r="56" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C56">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D56">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E56">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H56">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="I56" t="s">
-        <v>6</v>
-      </c>
-      <c r="S56" t="s">
+        <v>3</v>
+      </c>
+      <c r="P56" t="s">
         <v>133</v>
       </c>
       <c r="Z56" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AA56" s="2">
         <v>0</v>
       </c>
       <c r="AB56" s="2">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AC56" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AD56" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AE56">
         <v>120000</v>
       </c>
       <c r="AF56">
-        <v>11000</v>
+        <v>1250</v>
       </c>
       <c r="AG56">
         <v>5</v>
@@ -6278,7 +6290,7 @@
         <v>1</v>
       </c>
       <c r="AJ56" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="s">
         <v>129</v>
@@ -6289,7 +6301,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -6301,7 +6313,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>86883</v>
+        <v>47560</v>
       </c>
       <c r="AN56">
         <v>4</v>
@@ -6309,13 +6321,13 @@
     </row>
     <row r="57" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C57">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D57">
         <v>15</v>
@@ -6327,40 +6339,40 @@
         <v>2</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H57">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="I57" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" t="s">
+        <v>29</v>
+      </c>
+      <c r="L57" t="s">
         <v>133</v>
       </c>
       <c r="Z57" s="2">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="AA57" s="2">
         <v>0</v>
       </c>
       <c r="AB57" s="2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AC57" s="2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD57" s="2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE57">
-        <v>120000</v>
+        <v>70000</v>
       </c>
       <c r="AF57">
-        <v>1250</v>
+        <v>400</v>
       </c>
       <c r="AG57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH57" s="1">
         <v>3.5</v>
@@ -6372,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="AL57" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AM57" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6380,7 +6392,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -6392,7 +6404,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>92560</v>
+        <v>52000</v>
       </c>
       <c r="AN57">
         <v>4</v>
@@ -6400,55 +6412,52 @@
     </row>
     <row r="58" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A58">
+        <v>34</v>
+      </c>
+      <c r="B58" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58">
+        <v>250</v>
+      </c>
+      <c r="D58">
+        <v>20</v>
+      </c>
+      <c r="E58">
         <v>15</v>
       </c>
-      <c r="B58" t="s">
-        <v>44</v>
-      </c>
-      <c r="C58">
-        <v>300</v>
-      </c>
-      <c r="D58">
-        <v>15</v>
-      </c>
-      <c r="E58">
-        <v>30</v>
-      </c>
       <c r="F58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="H58">
+        <v>150</v>
+      </c>
+      <c r="I58" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="AA58" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AB58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AD58" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AE58">
+        <v>40000</v>
+      </c>
+      <c r="AF58">
         <v>200</v>
-      </c>
-      <c r="I58" t="s">
-        <v>29</v>
-      </c>
-      <c r="L58" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z58" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="AA58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE58">
-        <v>70000</v>
-      </c>
-      <c r="AF58">
-        <v>400</v>
       </c>
       <c r="AG58">
         <v>4</v>
@@ -6471,7 +6480,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -6483,7 +6492,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>97300</v>
+        <v>58362.5</v>
       </c>
       <c r="AN58">
         <v>4</v>
@@ -6491,55 +6500,58 @@
     </row>
     <row r="59" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
+        <v>36</v>
+      </c>
+      <c r="C59">
+        <v>200</v>
+      </c>
+      <c r="D59">
+        <v>12</v>
+      </c>
+      <c r="E59">
         <v>50</v>
       </c>
-      <c r="C59">
-        <v>250</v>
-      </c>
-      <c r="D59">
-        <v>20</v>
-      </c>
-      <c r="E59">
-        <v>15</v>
-      </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="H59">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="I59" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="S59" t="s">
+        <v>133</v>
       </c>
       <c r="Z59" s="2">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AA59" s="2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB59" s="2">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AC59" s="2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD59" s="2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE59">
-        <v>40000</v>
+        <v>120000</v>
       </c>
       <c r="AF59">
-        <v>200</v>
+        <v>11000</v>
       </c>
       <c r="AG59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH59" s="1">
         <v>3.5</v>
@@ -6548,10 +6560,10 @@
         <v>1</v>
       </c>
       <c r="AJ59" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL59" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AM59" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6559,7 +6571,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -6571,7 +6583,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>115037.5</v>
+        <v>60483</v>
       </c>
       <c r="AN59">
         <v>4</v>
@@ -6653,7 +6665,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -6665,7 +6677,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>119075</v>
+        <v>63075</v>
       </c>
       <c r="AN60">
         <v>4</v>
@@ -6673,58 +6685,61 @@
     </row>
     <row r="61" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C61">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D61">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E61">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G61">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H61">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="I61" t="s">
         <v>3</v>
       </c>
-      <c r="Y61" s="10" t="s">
+      <c r="J61" t="s">
+        <v>133</v>
+      </c>
+      <c r="N61" t="s">
         <v>133</v>
       </c>
       <c r="Z61" s="2">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="AA61" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AB61" s="2">
         <v>0</v>
       </c>
       <c r="AC61" s="2">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="AD61" s="2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE61">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>10250</v>
       </c>
       <c r="AG61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH61" s="1">
         <v>3.5</v>
@@ -6735,8 +6750,11 @@
       <c r="AJ61" t="s">
         <v>0</v>
       </c>
+      <c r="AK61" t="s">
+        <v>161</v>
+      </c>
       <c r="AL61" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AM61" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6744,7 +6762,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -6756,7 +6774,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>124820</v>
+        <v>63120</v>
       </c>
       <c r="AN61">
         <v>4</v>
@@ -6764,61 +6782,58 @@
     </row>
     <row r="62" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="B62" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C62">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="D62">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E62">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62">
+        <v>10</v>
+      </c>
+      <c r="H62">
+        <v>500</v>
+      </c>
+      <c r="I62" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z62" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="AA62" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AD62" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AE62">
+        <v>80000</v>
+      </c>
+      <c r="AF62">
+        <v>0</v>
+      </c>
+      <c r="AG62">
         <v>4</v>
-      </c>
-      <c r="G62">
-        <v>4</v>
-      </c>
-      <c r="H62">
-        <v>24</v>
-      </c>
-      <c r="I62" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" t="s">
-        <v>133</v>
-      </c>
-      <c r="N62" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z62" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="AA62" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="AB62" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="AD62" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE62">
-        <v>30000</v>
-      </c>
-      <c r="AF62">
-        <v>10250</v>
-      </c>
-      <c r="AG62">
-        <v>3</v>
       </c>
       <c r="AH62" s="1">
         <v>3.5</v>
@@ -6829,13 +6844,8 @@
       <c r="AJ62" t="s">
         <v>0</v>
       </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Boss for ID10</t>
-        </is>
-      </c>
       <c r="AL62" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AM62" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -6843,7 +6853,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -6855,7 +6865,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>124920</v>
+        <v>65470</v>
       </c>
       <c r="AN62">
         <v>4</v>
@@ -6863,43 +6873,40 @@
     </row>
     <row r="63" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C63">
-        <v>333</v>
+        <v>200</v>
       </c>
       <c r="D63">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E63">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F63">
+        <v>3</v>
+      </c>
+      <c r="G63">
         <v>6</v>
       </c>
-      <c r="G63">
-        <v>2</v>
-      </c>
       <c r="H63">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I63" t="s">
-        <v>3</v>
-      </c>
-      <c r="T63" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y63" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="O63" t="s">
         <v>133</v>
       </c>
       <c r="Z63" s="2">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AA63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB63" s="2">
         <v>0</v>
@@ -6911,13 +6918,13 @@
         <v>0</v>
       </c>
       <c r="AE63">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="AF63">
-        <v>3663</v>
+        <v>600</v>
       </c>
       <c r="AG63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH63" s="1">
         <v>3.5</v>
@@ -6927,6 +6934,9 @@
       </c>
       <c r="AJ63" t="s">
         <v>0</v>
+      </c>
+      <c r="AK63" t="s">
+        <v>162</v>
       </c>
       <c r="AL63" t="s">
         <v>127</v>
@@ -6937,7 +6947,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -6949,7 +6959,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>127706</v>
+        <v>66850</v>
       </c>
       <c r="AN63">
         <v>4</v>
@@ -6957,40 +6967,43 @@
     </row>
     <row r="64" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="B64" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64">
+        <v>333</v>
+      </c>
+      <c r="D64">
+        <v>16</v>
+      </c>
+      <c r="E64">
         <v>33</v>
       </c>
-      <c r="C64">
-        <v>200</v>
-      </c>
-      <c r="D64">
-        <v>30</v>
-      </c>
-      <c r="E64">
-        <v>50</v>
-      </c>
       <c r="F64">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G64">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I64" t="s">
-        <v>6</v>
-      </c>
-      <c r="O64" t="s">
+        <v>3</v>
+      </c>
+      <c r="T64" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y64" s="10" t="s">
         <v>133</v>
       </c>
       <c r="Z64" s="2">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AA64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB64" s="2">
         <v>0</v>
@@ -7002,13 +7015,13 @@
         <v>0</v>
       </c>
       <c r="AE64">
-        <v>120000</v>
+        <v>100000</v>
       </c>
       <c r="AF64">
-        <v>600</v>
+        <v>3663</v>
       </c>
       <c r="AG64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH64" s="1">
         <v>3.5</v>
@@ -7018,11 +7031,6 @@
       </c>
       <c r="AJ64" t="s">
         <v>0</v>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Boss for ID23</t>
-        </is>
       </c>
       <c r="AL64" t="s">
         <v>127</v>
@@ -7033,7 +7041,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -7045,7 +7053,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>128650</v>
+        <v>68432</v>
       </c>
       <c r="AN64">
         <v>4</v>
@@ -7124,7 +7132,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -7136,7 +7144,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>137780</v>
+        <v>71440</v>
       </c>
       <c r="AN65">
         <v>4</v>
@@ -7215,7 +7223,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -7227,7 +7235,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>138660</v>
+        <v>78660</v>
       </c>
       <c r="AN66">
         <v>4</v>
@@ -7309,7 +7317,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -7321,7 +7329,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>159520</v>
+        <v>81670</v>
       </c>
       <c r="AN67">
         <v>4</v>
@@ -7403,7 +7411,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -7415,7 +7423,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>179950</v>
+        <v>91950</v>
       </c>
       <c r="AN68">
         <v>4</v>
@@ -7497,7 +7505,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -7509,7 +7517,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>183790</v>
+        <v>93790</v>
       </c>
       <c r="AN69">
         <v>4</v>
@@ -7582,10 +7590,8 @@
       <c r="AJ70" t="s">
         <v>0</v>
       </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Boss for ID59</t>
-        </is>
+      <c r="AK70" t="s">
+        <v>163</v>
       </c>
       <c r="AL70" t="s">
         <v>130</v>
@@ -7596,7 +7602,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -7608,7 +7614,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>222360</v>
+        <v>112360</v>
       </c>
       <c r="AN70">
         <v>4</v>
@@ -7690,7 +7696,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -7702,7 +7708,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>259340</v>
+        <v>132840</v>
       </c>
       <c r="AN71">
         <v>4</v>
@@ -7784,7 +7790,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -7796,7 +7802,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>264180</v>
+        <v>139180</v>
       </c>
       <c r="AN72">
         <v>4</v>
@@ -7804,76 +7810,76 @@
     </row>
     <row r="73" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B73" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C73">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="D73">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E73">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F73">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="H73">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="I73" t="s">
-        <v>3</v>
-      </c>
-      <c r="J73" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q73" t="s">
+        <v>29</v>
+      </c>
+      <c r="K73" t="s">
+        <v>133</v>
+      </c>
+      <c r="L73" t="s">
         <v>133</v>
       </c>
       <c r="Y73" s="10" t="s">
         <v>133</v>
       </c>
       <c r="Z73" s="2">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AA73" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB73" s="2">
         <v>0</v>
       </c>
       <c r="AC73" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD73" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE73">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="AF73">
-        <v>8000</v>
+        <v>5600</v>
       </c>
       <c r="AG73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH73" s="1">
         <v>3.5</v>
       </c>
       <c r="AI73" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AJ73" t="s">
         <v>0</v>
       </c>
       <c r="AL73" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AM73" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -7881,7 +7887,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -7893,7 +7899,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>268900</v>
+        <v>145500</v>
       </c>
       <c r="AN73">
         <v>4</v>
@@ -7901,76 +7907,76 @@
     </row>
     <row r="74" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B74" t="s">
+        <v>41</v>
+      </c>
+      <c r="C74">
+        <v>375</v>
+      </c>
+      <c r="D74">
         <v>30</v>
       </c>
-      <c r="C74">
-        <v>400</v>
-      </c>
-      <c r="D74">
-        <v>35</v>
-      </c>
       <c r="E74">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G74">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="H74">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="I74" t="s">
-        <v>29</v>
-      </c>
-      <c r="K74" t="s">
-        <v>133</v>
-      </c>
-      <c r="L74" t="s">
+        <v>3</v>
+      </c>
+      <c r="J74" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q74" t="s">
         <v>133</v>
       </c>
       <c r="Y74" s="10" t="s">
         <v>133</v>
       </c>
       <c r="Z74" s="2">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AA74" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AB74" s="2">
         <v>0</v>
       </c>
       <c r="AC74" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AD74" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE74">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="AF74">
-        <v>5600</v>
+        <v>8000</v>
       </c>
       <c r="AG74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH74" s="1">
         <v>3.5</v>
       </c>
       <c r="AI74" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AJ74" t="s">
         <v>0</v>
       </c>
       <c r="AL74" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="AM74" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -7978,7 +7984,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -7990,7 +7996,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>286300</v>
+        <v>148900</v>
       </c>
       <c r="AN74">
         <v>5</v>
@@ -7998,61 +8004,58 @@
     </row>
     <row r="75" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C75">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D75">
         <v>30</v>
       </c>
       <c r="E75">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G75">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H75">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I75" t="s">
         <v>3</v>
       </c>
-      <c r="V75">
-        <v>0.1</v>
-      </c>
-      <c r="W75">
+      <c r="P75" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y75" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z75" s="2">
         <v>0.2</v>
       </c>
-      <c r="Y75" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z75" s="2">
-        <v>0.1</v>
-      </c>
       <c r="AA75" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AB75" s="2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AC75" s="2">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AD75" s="2">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AE75">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="AF75">
-        <v>8000</v>
+        <v>500</v>
       </c>
       <c r="AG75">
         <v>5</v>
@@ -8064,10 +8067,10 @@
         <v>1</v>
       </c>
       <c r="AJ75" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL75" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AM75" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -8075,7 +8078,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -8087,7 +8090,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>291425</v>
+        <v>159220</v>
       </c>
       <c r="AN75">
         <v>5</v>
@@ -8095,58 +8098,61 @@
     </row>
     <row r="76" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B76" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C76">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="D76">
         <v>30</v>
       </c>
       <c r="E76">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H76">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I76" t="s">
         <v>3</v>
       </c>
-      <c r="P76" t="s">
-        <v>133</v>
+      <c r="V76">
+        <v>0.1</v>
+      </c>
+      <c r="W76">
+        <v>0.2</v>
       </c>
       <c r="Y76" s="10" t="s">
         <v>133</v>
       </c>
       <c r="Z76" s="2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AA76" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AB76" s="2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AC76" s="2">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AD76" s="2">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AE76">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="AF76">
-        <v>500</v>
+        <v>8000</v>
       </c>
       <c r="AG76">
         <v>5</v>
@@ -8158,10 +8164,10 @@
         <v>1</v>
       </c>
       <c r="AJ76" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL76" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AM76" s="6">
         <f>(_csv247[[#This Row],[entity 1:
@@ -8169,7 +8175,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -8181,7 +8187,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>313220</v>
+        <v>159425</v>
       </c>
       <c r="AN76">
         <v>5</v>
@@ -8260,7 +8266,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -8272,7 +8278,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>363615</v>
+        <v>190295</v>
       </c>
       <c r="AN77">
         <v>5</v>
@@ -8351,7 +8357,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -8363,7 +8369,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>432900</v>
+        <v>221700</v>
       </c>
       <c r="AN78">
         <v>5</v>
@@ -8442,7 +8448,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -8454,7 +8460,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>475792</v>
+        <v>243358</v>
       </c>
       <c r="AN79">
         <v>5</v>
@@ -8524,10 +8530,8 @@
       <c r="AJ80" t="s">
         <v>0</v>
       </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Boss for ID13</t>
-        </is>
+      <c r="AK80" t="s">
+        <v>122</v>
       </c>
       <c r="AL80" t="s">
         <v>128</v>
@@ -8538,7 +8542,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -8550,7 +8554,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>525460</v>
+        <v>267460</v>
       </c>
       <c r="AN80">
         <v>5</v>
@@ -8629,7 +8633,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -8641,7 +8645,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>675100</v>
+        <v>345100</v>
       </c>
       <c r="AN81">
         <v>5</v>
@@ -8708,10 +8712,8 @@
       <c r="AJ82" t="s">
         <v>0</v>
       </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Boss for ID36</t>
-        </is>
+      <c r="AK82" t="s">
+        <v>164</v>
       </c>
       <c r="AL82" t="s">
         <v>130</v>
@@ -8722,7 +8724,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -8734,7 +8736,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>725000</v>
+        <v>373000</v>
       </c>
       <c r="AN82">
         <v>5</v>
@@ -8819,7 +8821,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -8831,7 +8833,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>749100</v>
+        <v>401900</v>
       </c>
       <c r="AN83">
         <v>5</v>
@@ -8916,7 +8918,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -8928,7 +8930,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>856593</v>
+        <v>448593</v>
       </c>
       <c r="AN84">
         <v>5</v>
@@ -9010,7 +9012,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -9022,7 +9024,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>1572700</v>
+        <v>792700</v>
       </c>
       <c r="AN85">
         <v>5</v>
@@ -9101,7 +9103,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -9113,7 +9115,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>1877573</v>
+        <v>967573</v>
       </c>
       <c r="AN86">
         <v>5</v>
@@ -9195,7 +9197,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -9207,7 +9209,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>2078500</v>
+        <v>1054500</v>
       </c>
       <c r="AN87">
         <v>5</v>
@@ -9286,7 +9288,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -9298,7 +9300,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>2302600</v>
+        <v>1259300</v>
       </c>
       <c r="AN88">
         <v>5</v>
@@ -9380,7 +9382,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -9392,7 +9394,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>2748300</v>
+        <v>1462200</v>
       </c>
       <c r="AN89">
         <v>5</v>
@@ -9474,7 +9476,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -9486,7 +9488,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>4152180</v>
+        <v>2098430</v>
       </c>
       <c r="AN90">
         <v>5</v>
@@ -9565,7 +9567,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -9577,7 +9579,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>4586360</v>
+        <v>2311360</v>
       </c>
       <c r="AN91">
         <v>5</v>
@@ -9656,7 +9658,7 @@
 armor]]+_csv247[[#This Row],[entity 1:
 health]]*SUM(_csv247[[#This Row],[entity 10:
 res_magic]:[entity 14:
-res_poison]]))*20+_csv247[[#This Row],[entity 3:
+res_poison]]))*10+_csv247[[#This Row],[entity 3:
 speed]]*_csv247[[#This Row],[entity 4:
 no_of_attacks (Melee only)]]*AVERAGE(_csv247[[#This Row],[entity 5:
 damage_min]:[entity 6:
@@ -9668,7 +9670,7 @@
 increases_magical_age_by_1_year_on_hit]])*4000+_csv247[[#This Row],[entity 8l: 
 regeneration_per_turn_in_percent_of total_life]]*100000+_csv247[[#This Row],[entity 8m: 
 steal_mana_on_hit_in_percent_of_characters_max_mana]]*50000</f>
-        <v>6230300</v>
+        <v>3150300</v>
       </c>
       <c r="AN92">
         <v>5</v>
@@ -9687,7 +9689,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
